--- a/examples/sample_output.xlsx
+++ b/examples/sample_output.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation_Comps" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation_EarlyStage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation_Patent" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="in_tam_usd">Inputs!$B$13</definedName>
@@ -78,6 +79,27 @@
     <definedName name="in_target_headcount_y3">Inputs!$B$75</definedName>
     <definedName name="in_avg_fully_loaded_cost">Inputs!$B$76</definedName>
     <definedName name="in_ai_automation_target">Inputs!$B$77</definedName>
+    <definedName name="in_esop_pool_pct">Inputs!$B$79</definedName>
+    <definedName name="in_founder1_time_pct">Inputs!$B$81</definedName>
+    <definedName name="in_founder1_capital_usd">Inputs!$B$82</definedName>
+    <definedName name="in_founder1_ip_score">Inputs!$B$83</definedName>
+    <definedName name="in_founder1_role_criticality">Inputs!$B$84</definedName>
+    <definedName name="in_founder1_salary_forgone_usd">Inputs!$B$85</definedName>
+    <definedName name="in_founder2_time_pct">Inputs!$B$87</definedName>
+    <definedName name="in_founder2_capital_usd">Inputs!$B$88</definedName>
+    <definedName name="in_founder2_ip_score">Inputs!$B$89</definedName>
+    <definedName name="in_founder2_role_criticality">Inputs!$B$90</definedName>
+    <definedName name="in_founder2_salary_forgone_usd">Inputs!$B$91</definedName>
+    <definedName name="in_founder3_time_pct">Inputs!$B$93</definedName>
+    <definedName name="in_founder3_capital_usd">Inputs!$B$94</definedName>
+    <definedName name="in_founder3_ip_score">Inputs!$B$95</definedName>
+    <definedName name="in_founder3_role_criticality">Inputs!$B$96</definedName>
+    <definedName name="in_founder3_salary_forgone_usd">Inputs!$B$97</definedName>
+    <definedName name="in_founder4_time_pct">Inputs!$B$99</definedName>
+    <definedName name="in_founder4_capital_usd">Inputs!$B$100</definedName>
+    <definedName name="in_founder4_ip_score">Inputs!$B$101</definedName>
+    <definedName name="in_founder4_role_criticality">Inputs!$B$102</definedName>
+    <definedName name="in_founder4_salary_forgone_usd">Inputs!$B$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,6 +226,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +626,7 @@
       </c>
       <c r="B4" s="3">
         <f>Scorecard!C16</f>
-        <v/>
+        <v>3.695</v>
       </c>
     </row>
     <row r="5">
@@ -614,7 +637,7 @@
       </c>
       <c r="B5" s="4">
         <f>Scorecard!C17</f>
-        <v/>
+        <v>67.375</v>
       </c>
     </row>
     <row r="6">
@@ -623,9 +646,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <f>Scorecard!C18</f>
-        <v/>
+        <v>GO</v>
       </c>
     </row>
     <row r="8">
@@ -636,7 +659,7 @@
       </c>
       <c r="B8" s="5">
         <f>Valuation_DCF!B19</f>
-        <v/>
+        <v>42672.16325</v>
       </c>
     </row>
     <row r="9">
@@ -647,7 +670,7 @@
       </c>
       <c r="B9" s="5">
         <f>Valuation_Comps!B5</f>
-        <v/>
+        <v>2500000</v>
       </c>
     </row>
     <row r="10">
@@ -658,7 +681,7 @@
       </c>
       <c r="B10" s="5">
         <f>Valuation_EarlyStage!B3</f>
-        <v/>
+        <v>1600000</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +692,7 @@
       </c>
       <c r="B11" s="5">
         <f>Valuation_EarlyStage!B4</f>
-        <v/>
+        <v>3079166.667</v>
       </c>
     </row>
     <row r="12">
@@ -680,7 +703,7 @@
       </c>
       <c r="B12" s="5">
         <f>Valuation_EarlyStage!B5</f>
-        <v/>
+        <v>6666666.667</v>
       </c>
     </row>
     <row r="13">
@@ -691,7 +714,7 @@
       </c>
       <c r="B13" s="5">
         <f>Valuation_EarlyStage!B9</f>
-        <v/>
+        <v>1973168.041</v>
       </c>
     </row>
     <row r="14">
@@ -702,7 +725,7 @@
       </c>
       <c r="B14" s="5">
         <f>Valuation_Patent!B7</f>
-        <v/>
+        <v>235567.5041</v>
       </c>
     </row>
     <row r="16">
@@ -713,7 +736,7 @@
       </c>
       <c r="B16" s="5">
         <f>Org!I23</f>
-        <v/>
+        <v>262500</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +747,7 @@
       </c>
       <c r="B17" s="5">
         <f>Org!J23</f>
-        <v/>
+        <v>882500</v>
       </c>
     </row>
   </sheetData>
@@ -733,6 +756,183 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Portfolio Screening (this idea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Edit yellow cells. Compare the four methods — divergence flags scoring sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Monetary impact ($/yr if successful)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adoption (0-1)</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Business critical (0-1)</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ownership (0 ext, 1 internal)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Risk PoS (0-1)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Time of replacement (yrs)</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Time to commercialize (yrs)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cost to develop ($)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Modified RICE</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>(B4*B5*B6*B7*B8*B9)/(B10*B11)</f>
+        <v>86.4</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Reach × Impact × Confidence / Effort (Samyama variant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>WSJF</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>(MIN(100,B4*B5*B8/100000)+MAX(0,MIN(1,1/MAX(B9,0.5)))*100+B6*100)/B10</f>
+        <v>106.6666667</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>(BV + TimeCriticality + RiskReduction) / Duration  [SAFe]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>CD3 ($/yr per yr)</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>(B4*B5*B8)/B10</f>
+        <v>9000000</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Cost of Delay / Duration  [Reinertsen]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>EMV (USD)</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>B8*(B4*B5)*B9-B11</f>
+        <v>53750000</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PoS × (annual value × life) − cost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1169,17 +1369,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Rubric category</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>RICE/WSJF mapping</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Cross-check</t>
         </is>
@@ -1315,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2275,271 @@
       </c>
       <c r="B77" s="12" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>ESOP / option pool size</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 name</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Founder A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 time commitment (0-1)</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 cash contributed (USD)</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 IP / prior work (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 role criticality (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Founder 1 annual salary forgone (USD)</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 name</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Founder B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 time commitment (0-1)</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 cash contributed (USD)</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 IP / prior work (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 role criticality (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>Founder 2 annual salary forgone (USD)</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 name</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Founder C</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 time commitment (0-1)</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 cash contributed (USD)</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 IP / prior work (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 role criticality (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Founder 3 annual salary forgone (USD)</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 name</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Founder D</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 time commitment (0-1)</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 cash contributed (USD)</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 IP / prior work (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 role criticality (1-5, 0 if N/A)</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Founder 4 annual salary forgone (USD)</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2602,7 @@
       </c>
       <c r="C4" s="3">
         <f>AVERAGE(in_score_problem_severity,in_score_problem_frequency,in_score_willingness_to_pay)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
@@ -2156,7 +2621,7 @@
       </c>
       <c r="C5" s="3">
         <f>AVERAGE(in_score_market_timing)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
@@ -2175,7 +2640,7 @@
       </c>
       <c r="C6" s="3">
         <f>AVERAGE(in_score_moat_tech,in_score_moat_data,in_score_moat_brand,in_score_ip_strength)</f>
-        <v/>
+        <v>2.75</v>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
@@ -2194,7 +2659,7 @@
       </c>
       <c r="C7" s="3">
         <f>AVERAGE(in_score_team_domain,in_score_team_execution,in_score_team_completeness)</f>
-        <v/>
+        <v>3.333333333</v>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
@@ -2213,7 +2678,7 @@
       </c>
       <c r="C8" s="3">
         <f>AVERAGE(in_score_gtm_clarity)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
@@ -2232,7 +2697,7 @@
       </c>
       <c r="C9" s="3">
         <f>AVERAGE(in_score_unit_economics,in_score_capital_efficiency)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
@@ -2251,7 +2716,7 @@
       </c>
       <c r="C10" s="3">
         <f>AVERAGE(in_score_scalability)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
@@ -2270,7 +2735,7 @@
       </c>
       <c r="C11" s="3">
         <f>AVERAGE(in_score_regulatory_risk)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
@@ -2289,7 +2754,7 @@
       </c>
       <c r="C12" s="3">
         <f>AVERAGE(in_score_ai_resilience)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
@@ -2305,7 +2770,7 @@
       </c>
       <c r="C14" s="3">
         <f>SUMPRODUCT(B4:B12,C4:C12)</f>
-        <v/>
+        <v>3.545</v>
       </c>
     </row>
     <row r="15">
@@ -2316,7 +2781,7 @@
       </c>
       <c r="C15" s="3">
         <f>MAX(-1,MIN(1,LOG10(MAX(1,in_tam_usd)/1000000000)))*0.15</f>
-        <v/>
+        <v>0.15</v>
       </c>
     </row>
     <row r="16">
@@ -2327,7 +2792,7 @@
       </c>
       <c r="C16" s="3">
         <f>MAX(1,MIN(5,C14+C15))</f>
-        <v/>
+        <v>3.695</v>
       </c>
     </row>
     <row r="17">
@@ -2338,7 +2803,7 @@
       </c>
       <c r="C17" s="4">
         <f>(C16-1)/4*100</f>
-        <v/>
+        <v>67.375</v>
       </c>
     </row>
     <row r="18">
@@ -2347,9 +2812,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C18">
+      <c r="C18" t="str">
         <f>IF(C17&gt;=75,"STRONG GO",IF(C17&gt;=60,"GO",IF(C17&gt;=45,"CONDITIONAL",IF(C17&gt;=30,"WEAK","NO-GO"))))</f>
-        <v/>
+        <v>GO</v>
       </c>
     </row>
   </sheetData>
@@ -2455,15 +2920,15 @@
       </c>
       <c r="D4">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E4">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F4" s="18">
         <f>ROUND(0.2*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.32</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2477,11 +2942,11 @@
       </c>
       <c r="I4" s="5">
         <f>D4*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J4" s="5">
         <f>E4*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="5">
@@ -2492,7 +2957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CTO / Co-founder</t>
+          <t>CTO / Chief AI Architect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2502,15 +2967,15 @@
       </c>
       <c r="D5">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E5">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F5" s="18">
         <f>ROUND(0.3*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2524,11 +2989,11 @@
       </c>
       <c r="I5" s="5">
         <f>D5*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J5" s="5">
         <f>E5*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="6">
@@ -2539,7 +3004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COO / Head of Ops</t>
+          <t>Head of Autonomous Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2549,15 +3014,15 @@
       </c>
       <c r="D6">
         <f>ROUND(0.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E6">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F6" s="18">
         <f>ROUND(0.4*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.46</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2566,16 +3031,16 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>AI-run dashboards, automated reporting, exception-only escalation.</t>
+          <t>AI-run dashboards, automated reporting, exception-only escalation; designs the human-in-the-loop seams.</t>
         </is>
       </c>
       <c r="I6" s="5">
         <f>D6*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
         <f>E6*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="7">
@@ -2586,7 +3051,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>Head of Product (AI-Native)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2596,15 +3061,15 @@
       </c>
       <c r="D7">
         <f>ROUND(0.5/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="E7">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F7" s="18">
         <f>ROUND(0.3*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2618,11 +3083,11 @@
       </c>
       <c r="I7" s="5">
         <f>D7*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="J7" s="5">
         <f>E7*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="8">
@@ -2633,7 +3098,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2643,15 +3108,15 @@
       </c>
       <c r="D8">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E8">
         <f>ROUND(2.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="F8" s="18">
         <f>ROUND(0.4*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.46</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2660,16 +3125,16 @@
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>Spec drafting via AI, automatic competitive scans, user-interview transcription+coding.</t>
+          <t>Ships, not just specs: AI-assisted prototypes, transcript coding, competitive scans.</t>
         </is>
       </c>
       <c r="I8" s="5">
         <f>D8*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J8" s="5">
         <f>E8*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>57500</v>
       </c>
     </row>
     <row r="9">
@@ -2680,7 +3145,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Product Designer (AI-Augmented)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2690,15 +3155,15 @@
       </c>
       <c r="D9">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E9">
         <f>ROUND(2.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="F9" s="18">
         <f>ROUND(0.5*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.53</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2712,11 +3177,11 @@
       </c>
       <c r="I9" s="5">
         <f>D9*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J9" s="5">
         <f>E9*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>57500</v>
       </c>
     </row>
     <row r="10">
@@ -2727,7 +3192,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eng Lead / Architect</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2737,15 +3202,15 @@
       </c>
       <c r="D10">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E10">
         <f>ROUND(1.5/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.8</v>
       </c>
       <c r="F10" s="18">
         <f>ROUND(0.25*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.36</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2754,16 +3219,16 @@
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>AI architecture critic, automated design-doc review.</t>
+          <t>AI architecture critic, automated design-doc review, owns the eval+observability spine.</t>
         </is>
       </c>
       <c r="I10" s="5">
         <f>D10*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J10" s="5">
         <f>E10*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>45000</v>
       </c>
     </row>
     <row r="11">
@@ -2774,7 +3239,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Senior Engineer (full-stack)</t>
+          <t>Forward-Deployed AI Engineer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2784,33 +3249,33 @@
       </c>
       <c r="D11">
         <f>ROUND(2.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="E11">
         <f>ROUND(4.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="F11" s="18">
         <f>ROUND(0.55*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.56</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eng Lead</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>Claude/Copilot pair-programming, AI test-gen, AI code review on PRs.</t>
+          <t>Claude/Copilot pair-programming, AI test-gen, AI code review on PRs, deploys with customers.</t>
         </is>
       </c>
       <c r="I11" s="5">
         <f>D11*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>37500</v>
       </c>
       <c r="J11" s="5">
         <f>E11*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>117500</v>
       </c>
     </row>
     <row r="12">
@@ -2821,7 +3286,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ML / Applied AI Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2831,33 +3296,33 @@
       </c>
       <c r="D12">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E12">
         <f>ROUND(2.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="F12" s="18">
         <f>ROUND(0.4*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.46</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eng Lead</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>Owns the model layer; uses AI for eval harness, dataset curation, prompt tuning.</t>
+          <t>Owns the model layer; eval harness, dataset curation, prompt + retrieval tuning.</t>
         </is>
       </c>
       <c r="I12" s="5">
         <f>D12*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J12" s="5">
         <f>E12*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>57500</v>
       </c>
     </row>
     <row r="13">
@@ -2868,7 +3333,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DevOps / Platform</t>
+          <t>Platform / AI-Ops Engineer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2878,33 +3343,33 @@
       </c>
       <c r="D13">
         <f>ROUND(0.5/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="E13">
         <f>ROUND(1.5/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.8</v>
       </c>
       <c r="F13" s="18">
         <f>ROUND(0.6*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eng Lead</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>IaC generation, runbook automation, AI-driven incident triage.</t>
+          <t>IaC generation, runbook automation, AI-driven incident triage, agent infra.</t>
         </is>
       </c>
       <c r="I13" s="5">
         <f>D13*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="J13" s="5">
         <f>E13*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>45000</v>
       </c>
     </row>
     <row r="14">
@@ -2915,7 +3380,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Eval &amp; Quality Engineer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2925,33 +3390,33 @@
       </c>
       <c r="D14">
         <f>ROUND(0.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E14">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F14" s="18">
         <f>ROUND(0.7*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.67</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eng Lead</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Mostly AI-generated/maintained test suites; humans curate edge cases.</t>
+          <t>Owns LLM evals + property tests; humans curate edge cases that agents miss.</t>
         </is>
       </c>
       <c r="I14" s="5">
         <f>D14*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J14" s="5">
         <f>E14*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="15">
@@ -2962,7 +3427,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data / Analytics Lead</t>
+          <t>Decision Intelligence Lead</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2972,15 +3437,15 @@
       </c>
       <c r="D15">
         <f>ROUND(0.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F15" s="18">
         <f>ROUND(0.5*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.53</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2989,16 +3454,16 @@
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>Natural-language analytics, AI-built dashboards, anomaly detection.</t>
+          <t>Natural-language analytics, AI-built dashboards, anomaly detection, causal experimentation.</t>
         </is>
       </c>
       <c r="I15" s="5">
         <f>D15*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J15" s="5">
         <f>E15*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="16">
@@ -3009,7 +3474,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Head of GTM / Sales</t>
+          <t>Head of Revenue (AI-Native)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3019,15 +3484,15 @@
       </c>
       <c r="D16">
         <f>ROUND(0.5/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="E16">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F16" s="18">
         <f>ROUND(0.3*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3041,11 +3506,11 @@
       </c>
       <c r="I16" s="5">
         <f>D16*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="J16" s="5">
         <f>E16*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="17">
@@ -3056,7 +3521,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Forward-Deployed Account Lead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3066,33 +3531,33 @@
       </c>
       <c r="D17">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E17">
         <f>ROUND(3.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="F17" s="18">
         <f>ROUND(0.4*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.46</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Head of GTM</t>
+          <t>Head of Revenue</t>
         </is>
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>AI prospecting, personalized outbound at scale, post-call CRM automation.</t>
+          <t>AI prospecting, personalized outbound at scale, configures the customer's agent stack on-site.</t>
         </is>
       </c>
       <c r="I17" s="5">
         <f>D17*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J17" s="5">
         <f>E17*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>87500</v>
       </c>
     </row>
     <row r="18">
@@ -3103,7 +3568,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Growth / Marketing</t>
+          <t>Growth Engineer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3113,19 +3578,19 @@
       </c>
       <c r="D18">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E18">
         <f>ROUND(2.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="F18" s="18">
         <f>ROUND(0.6*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Head of GTM</t>
+          <t>Head of Revenue</t>
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr">
@@ -3135,11 +3600,11 @@
       </c>
       <c r="I18" s="5">
         <f>D18*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J18" s="5">
         <f>E18*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>57500</v>
       </c>
     </row>
     <row r="19">
@@ -3150,7 +3615,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Customer Outcomes Engineer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3160,33 +3625,33 @@
       </c>
       <c r="D19">
         <f>ROUND(1.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="E19">
         <f>ROUND(2.5/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>2.9</v>
       </c>
       <c r="F19" s="18">
         <f>ROUND(0.55*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.56</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Head of GTM</t>
+          <t>Head of Revenue</t>
         </is>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>AI-drafted QBRs, churn prediction, deflection via AI agents on T1 issues.</t>
+          <t>AI-drafted QBRs, churn prediction, T1 deflection by AI agents, escalation on intent.</t>
         </is>
       </c>
       <c r="I19" s="5">
         <f>D19*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>20000</v>
       </c>
       <c r="J19" s="5">
         <f>E19*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>72500</v>
       </c>
     </row>
     <row r="20">
@@ -3197,7 +3662,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Finance / FP&amp;A</t>
+          <t>Finance Engineer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3207,33 +3672,33 @@
       </c>
       <c r="D20">
         <f>ROUND(0.0/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E20">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F20" s="18">
         <f>ROUND(0.65*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.64</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>Head of Autonomous Ops</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>AI-built models, automated month-end, expense classification.</t>
+          <t>AI-built models, automated month-end, expense classification, scenario engines.</t>
         </is>
       </c>
       <c r="I20" s="5">
         <f>D20*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J20" s="5">
         <f>E20*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="21">
@@ -3244,7 +3709,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>People / Talent</t>
+          <t>Talent &amp; Team-Design Lead</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3254,33 +3719,33 @@
       </c>
       <c r="D21">
         <f>ROUND(0.5/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="E21">
         <f>ROUND(1.0/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="F21" s="18">
         <f>ROUND(0.5*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.53</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>Head of Autonomous Ops</t>
         </is>
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>AI-screened pipelines, structured-interview kits, onboarding bots.</t>
+          <t>AI-screened pipelines, structured-interview kits, onboarding bots, org-shape continuous design.</t>
         </is>
       </c>
       <c r="I21" s="5">
         <f>D21*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="J21" s="5">
         <f>E21*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>30000</v>
       </c>
     </row>
     <row r="22">
@@ -3291,7 +3756,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Legal / Compliance (frac)</t>
+          <t>Counsel (Fractional, AI-Assisted)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3301,15 +3766,15 @@
       </c>
       <c r="D22">
         <f>ROUND(0.2/13.2*in_target_headcount_y1,1)</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="E22">
         <f>ROUND(0.5/30.0*in_target_headcount_y3,1)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="F22" s="18">
         <f>ROUND(0.55*0.7+in_ai_automation_target*0.3,2)</f>
-        <v/>
+        <v>0.56</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3318,16 +3783,16 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>Fractional; AI-drafted contracts and policy redlines, human review.</t>
+          <t>Fractional; AI-drafted contracts and policy redlines, human review on novel terms.</t>
         </is>
       </c>
       <c r="I22" s="5">
         <f>D22*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="J22" s="5">
         <f>E22*in_avg_fully_loaded_cost</f>
-        <v/>
+        <v>15000</v>
       </c>
     </row>
     <row r="23">
@@ -3338,19 +3803,19 @@
       </c>
       <c r="D23" s="4">
         <f>SUM(D4:D22)</f>
-        <v/>
+        <v>10.5</v>
       </c>
       <c r="E23" s="4">
         <f>SUM(E4:E22)</f>
-        <v/>
+        <v>35.3</v>
       </c>
       <c r="I23" s="5">
         <f>SUM(I4:I22)</f>
-        <v/>
+        <v>262500</v>
       </c>
       <c r="J23" s="5">
         <f>SUM(J4:J22)</f>
-        <v/>
+        <v>882500</v>
       </c>
     </row>
   </sheetData>
@@ -3422,23 +3887,23 @@
       </c>
       <c r="B4" s="5">
         <f>in_rev_y1</f>
-        <v/>
+        <v>80000</v>
       </c>
       <c r="C4" s="5">
         <f>B4*(1+in_rev_growth_y2)</f>
-        <v/>
+        <v>280000</v>
       </c>
       <c r="D4" s="5">
         <f>C4*(1+in_rev_growth_y3)</f>
-        <v/>
+        <v>784000</v>
       </c>
       <c r="E4" s="5">
         <f>D4*(1+in_rev_growth_y4)</f>
-        <v/>
+        <v>1646400</v>
       </c>
       <c r="F4" s="5">
         <f>E4*(1+in_rev_growth_y5)</f>
-        <v/>
+        <v>2798880</v>
       </c>
     </row>
     <row r="5">
@@ -3449,23 +3914,23 @@
       </c>
       <c r="B5" s="5">
         <f>B4*in_gross_margin</f>
-        <v/>
+        <v>52000</v>
       </c>
       <c r="C5" s="5">
         <f>C4*in_gross_margin</f>
-        <v/>
+        <v>182000</v>
       </c>
       <c r="D5" s="5">
         <f>D4*in_gross_margin</f>
-        <v/>
+        <v>509600</v>
       </c>
       <c r="E5" s="5">
         <f>E4*in_gross_margin</f>
-        <v/>
+        <v>1070160</v>
       </c>
       <c r="F5" s="5">
         <f>F4*in_gross_margin</f>
-        <v/>
+        <v>1819272</v>
       </c>
     </row>
     <row r="6">
@@ -3476,23 +3941,23 @@
       </c>
       <c r="B6" s="5">
         <f>B4*in_opex_pct_rev</f>
-        <v/>
+        <v>44000</v>
       </c>
       <c r="C6" s="5">
         <f>C4*in_opex_pct_rev</f>
-        <v/>
+        <v>154000</v>
       </c>
       <c r="D6" s="5">
         <f>D4*in_opex_pct_rev</f>
-        <v/>
+        <v>431200</v>
       </c>
       <c r="E6" s="5">
         <f>E4*in_opex_pct_rev</f>
-        <v/>
+        <v>905520</v>
       </c>
       <c r="F6" s="5">
         <f>F4*in_opex_pct_rev</f>
-        <v/>
+        <v>1539384</v>
       </c>
     </row>
     <row r="7">
@@ -3503,23 +3968,23 @@
       </c>
       <c r="B7" s="5">
         <f>B5-B6</f>
-        <v/>
+        <v>8000</v>
       </c>
       <c r="C7" s="5">
         <f>C5-C6</f>
-        <v/>
+        <v>28000</v>
       </c>
       <c r="D7" s="5">
         <f>D5-D6</f>
-        <v/>
+        <v>78400</v>
       </c>
       <c r="E7" s="5">
         <f>E5-E6</f>
-        <v/>
+        <v>164640</v>
       </c>
       <c r="F7" s="5">
         <f>F5-F6</f>
-        <v/>
+        <v>279888</v>
       </c>
     </row>
     <row r="8">
@@ -3530,23 +3995,23 @@
       </c>
       <c r="B8" s="5">
         <f>B7*(1-in_tax_rate)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="C8" s="5">
         <f>C7*(1-in_tax_rate)</f>
-        <v/>
+        <v>21000</v>
       </c>
       <c r="D8" s="5">
         <f>D7*(1-in_tax_rate)</f>
-        <v/>
+        <v>58800</v>
       </c>
       <c r="E8" s="5">
         <f>E7*(1-in_tax_rate)</f>
-        <v/>
+        <v>123480</v>
       </c>
       <c r="F8" s="5">
         <f>F7*(1-in_tax_rate)</f>
-        <v/>
+        <v>209916</v>
       </c>
     </row>
     <row r="9">
@@ -3557,23 +4022,23 @@
       </c>
       <c r="B9" s="5">
         <f>B4*in_capex_pct_rev</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="C9" s="5">
         <f>C4*in_capex_pct_rev</f>
-        <v/>
+        <v>11200</v>
       </c>
       <c r="D9" s="5">
         <f>D4*in_capex_pct_rev</f>
-        <v/>
+        <v>31360</v>
       </c>
       <c r="E9" s="5">
         <f>E4*in_capex_pct_rev</f>
-        <v/>
+        <v>65856</v>
       </c>
       <c r="F9" s="5">
         <f>F4*in_capex_pct_rev</f>
-        <v/>
+        <v>111955.2</v>
       </c>
     </row>
     <row r="10">
@@ -3584,23 +4049,23 @@
       </c>
       <c r="B10" s="5">
         <f>B4*in_nwc_pct_rev</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="C10" s="5">
         <f>C4*in_nwc_pct_rev</f>
-        <v/>
+        <v>16800</v>
       </c>
       <c r="D10" s="5">
         <f>D4*in_nwc_pct_rev</f>
-        <v/>
+        <v>47040</v>
       </c>
       <c r="E10" s="5">
         <f>E4*in_nwc_pct_rev</f>
-        <v/>
+        <v>98784</v>
       </c>
       <c r="F10" s="5">
         <f>F4*in_nwc_pct_rev</f>
-        <v/>
+        <v>167932.8</v>
       </c>
     </row>
     <row r="11">
@@ -3611,23 +4076,23 @@
       </c>
       <c r="B11" s="5">
         <f>B10</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="C11" s="5">
         <f>C10-B10</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D11" s="5">
         <f>D10-C10</f>
-        <v/>
+        <v>30240</v>
       </c>
       <c r="E11" s="5">
         <f>E10-D10</f>
-        <v/>
+        <v>51744</v>
       </c>
       <c r="F11" s="5">
         <f>F10-E10</f>
-        <v/>
+        <v>69148.8</v>
       </c>
     </row>
     <row r="12">
@@ -3638,23 +4103,23 @@
       </c>
       <c r="B12" s="5">
         <f>B8-B9-B11</f>
-        <v/>
+        <v>-2000</v>
       </c>
       <c r="C12" s="5">
         <f>C8-C9-C11</f>
-        <v/>
+        <v>-2200</v>
       </c>
       <c r="D12" s="5">
         <f>D8-D9-D11</f>
-        <v/>
+        <v>-2800</v>
       </c>
       <c r="E12" s="5">
         <f>E8-E9-E11</f>
-        <v/>
+        <v>5880</v>
       </c>
       <c r="F12" s="5">
         <f>F8-F9-F11</f>
-        <v/>
+        <v>28812</v>
       </c>
     </row>
     <row r="13">
@@ -3665,23 +4130,23 @@
       </c>
       <c r="B13" s="19">
         <f>1/(1+in_discount_rate)^1</f>
-        <v/>
+        <v>0.78125</v>
       </c>
       <c r="C13" s="19">
         <f>1/(1+in_discount_rate)^2</f>
-        <v/>
+        <v>0.6103515625</v>
       </c>
       <c r="D13" s="19">
         <f>1/(1+in_discount_rate)^3</f>
-        <v/>
+        <v>0.4768371582</v>
       </c>
       <c r="E13" s="19">
         <f>1/(1+in_discount_rate)^4</f>
-        <v/>
+        <v>0.3725290298</v>
       </c>
       <c r="F13" s="19">
         <f>1/(1+in_discount_rate)^5</f>
-        <v/>
+        <v>0.2910383046</v>
       </c>
     </row>
     <row r="14">
@@ -3692,23 +4157,23 @@
       </c>
       <c r="B14" s="5">
         <f>B12*B13</f>
-        <v/>
+        <v>-1562.5</v>
       </c>
       <c r="C14" s="5">
         <f>C12*C13</f>
-        <v/>
+        <v>-1342.773438</v>
       </c>
       <c r="D14" s="5">
         <f>D12*D13</f>
-        <v/>
+        <v>-1335.144043</v>
       </c>
       <c r="E14" s="5">
         <f>E12*E13</f>
-        <v/>
+        <v>2190.470695</v>
       </c>
       <c r="F14" s="5">
         <f>F12*F13</f>
-        <v/>
+        <v>8385.395631</v>
       </c>
     </row>
     <row r="16">
@@ -3719,7 +4184,7 @@
       </c>
       <c r="B16" s="5">
         <f>F12*(1+in_terminal_growth)/(in_discount_rate-in_terminal_growth)</f>
-        <v/>
+        <v>124852</v>
       </c>
     </row>
     <row r="17">
@@ -3730,7 +4195,7 @@
       </c>
       <c r="B17" s="5">
         <f>B16/(1+in_discount_rate)^5</f>
-        <v/>
+        <v>36336.7144</v>
       </c>
     </row>
     <row r="18">
@@ -3741,7 +4206,7 @@
       </c>
       <c r="B18" s="5">
         <f>SUM(B14:F14)+B17</f>
-        <v/>
+        <v>42672.16325</v>
       </c>
     </row>
     <row r="19">
@@ -3752,7 +4217,7 @@
       </c>
       <c r="B19" s="5">
         <f>B18-in_net_debt_usd</f>
-        <v/>
+        <v>42672.16325</v>
       </c>
     </row>
   </sheetData>
@@ -3788,7 +4253,7 @@
       </c>
       <c r="B3" s="5">
         <f>in_comp_rev_multiple*in_comp_ntm_revenue</f>
-        <v/>
+        <v>4200000</v>
       </c>
     </row>
     <row r="4">
@@ -3799,7 +4264,7 @@
       </c>
       <c r="B4" s="5">
         <f>in_comp_ebitda_multiple*in_comp_ntm_ebitda</f>
-        <v/>
+        <v>800000</v>
       </c>
     </row>
     <row r="5">
@@ -3810,7 +4275,7 @@
       </c>
       <c r="B5" s="5">
         <f>AVERAGE(B3:B4)</f>
-        <v/>
+        <v>2500000</v>
       </c>
     </row>
   </sheetData>
@@ -3846,7 +4311,7 @@
       </c>
       <c r="B3" s="5">
         <f>in_berkus_idea+in_berkus_prototype+in_berkus_team+in_berkus_relationships+in_berkus_sales</f>
-        <v/>
+        <v>1600000</v>
       </c>
     </row>
     <row r="4">
@@ -3857,7 +4322,7 @@
       </c>
       <c r="B4" s="5">
         <f>in_scorecard_avg_premoney*Scorecard!C16/3</f>
-        <v/>
+        <v>3079166.667</v>
       </c>
     </row>
     <row r="5">
@@ -3868,7 +4333,7 @@
       </c>
       <c r="B5" s="5">
         <f>in_vc_exit_value/in_vc_target_roi</f>
-        <v/>
+        <v>6666666.667</v>
       </c>
     </row>
     <row r="6">
@@ -3879,7 +4344,7 @@
       </c>
       <c r="B6" s="5">
         <f>MAX(Valuation_DCF!B19,Valuation_Comps!B5)*1.5</f>
-        <v/>
+        <v>3750000</v>
       </c>
     </row>
     <row r="7">
@@ -3890,7 +4355,7 @@
       </c>
       <c r="B7" s="5">
         <f>AVERAGE(Valuation_DCF!B19,Valuation_Comps!B5)</f>
-        <v/>
+        <v>1271336.082</v>
       </c>
     </row>
     <row r="8">
@@ -3901,7 +4366,7 @@
       </c>
       <c r="B8" s="5">
         <f>B3</f>
-        <v/>
+        <v>1600000</v>
       </c>
     </row>
     <row r="9">
@@ -3912,7 +4377,7 @@
       </c>
       <c r="B9" s="5">
         <f>0.25*B6+0.5*B7+0.25*B8</f>
-        <v/>
+        <v>1973168.041</v>
       </c>
     </row>
   </sheetData>
@@ -3948,7 +4413,7 @@
       </c>
       <c r="B3" s="5">
         <f>in_patent_dev_cost_usd</f>
-        <v/>
+        <v>150000</v>
       </c>
     </row>
     <row r="4">
@@ -3959,7 +4424,7 @@
       </c>
       <c r="B4" s="5">
         <f>in_patent_comparable_sale_usd</f>
-        <v/>
+        <v>400000</v>
       </c>
     </row>
     <row r="5">
@@ -3970,7 +4435,7 @@
       </c>
       <c r="B5" s="5">
         <f>in_patent_royalty_rate*in_patent_revenue_attributable*(1-(1+in_discount_rate)^-in_patent_useful_life_years)/in_discount_rate</f>
-        <v/>
+        <v>65378.33609</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +4446,7 @@
       </c>
       <c r="B6" s="5">
         <f>0.20*in_patent_revenue_attributable*(1-(1+in_discount_rate)^-in_patent_useful_life_years)/in_discount_rate</f>
-        <v/>
+        <v>326891.6805</v>
       </c>
     </row>
     <row r="7">
@@ -3992,7 +4457,7 @@
       </c>
       <c r="B7" s="5">
         <f>AVERAGE(B3:B6)</f>
-        <v/>
+        <v>235567.5041</v>
       </c>
     </row>
   </sheetData>
@@ -4006,170 +4471,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Screening (this idea)</t>
+          <t>Founder Equity Split (Slicing-Pie style)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Edit yellow cells. Compare the four methods — divergence flags scoring sensitivity.</t>
+          <t>Units = time%·salary_forgone + capital + ip_score·100k + role_criticality·50k. Edit Inputs sheet — this recomputes.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Monetary impact ($/yr if successful)</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>60000000</v>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Time %</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Salary forgone</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>IP score</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Role criticality</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Final equity %</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Adoption (0-1)</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>0.5</v>
+      <c r="A5" t="str">
+        <f>Inputs!$B$80</f>
+        <v>Founder A</v>
+      </c>
+      <c r="B5" s="18">
+        <f>in_founder1_time_pct</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <f>in_founder1_salary_forgone_usd</f>
+        <v>100000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>in_founder1_capital_usd</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>in_founder1_ip_score</f>
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <f>in_founder1_role_criticality</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <f>B5*C5+D5+E5*100000+F5*50000</f>
+        <v>600000</v>
+      </c>
+      <c r="H5" s="20">
+        <f>IF($G$9=0,0,G5/$G$9*(1-in_esop_pool_pct))</f>
+        <v>0.425</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Business critical (0-1)</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="n">
-        <v>0.8</v>
+      <c r="A6" t="str">
+        <f>Inputs!$B$86</f>
+        <v>Founder B</v>
+      </c>
+      <c r="B6" s="18">
+        <f>in_founder2_time_pct</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <f>in_founder2_salary_forgone_usd</f>
+        <v>100000</v>
+      </c>
+      <c r="D6" s="5">
+        <f>in_founder2_capital_usd</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>in_founder2_ip_score</f>
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <f>in_founder2_role_criticality</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="5">
+        <f>B6*C6+D6+E6*100000+F6*50000</f>
+        <v>600000</v>
+      </c>
+      <c r="H6" s="20">
+        <f>IF($G$9=0,0,G6/$G$9*(1-in_esop_pool_pct))</f>
+        <v>0.425</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ownership (0 ext, 1 internal)</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" t="str">
+        <f>Inputs!$B$92</f>
+        <v>Founder C</v>
+      </c>
+      <c r="B7" s="18">
+        <f>in_founder3_time_pct</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <f>in_founder3_salary_forgone_usd</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <f>in_founder3_capital_usd</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>in_founder3_ip_score</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>in_founder3_role_criticality</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f>B7*C7+D7+E7*100000+F7*50000</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
+        <f>IF($G$9=0,0,G7/$G$9*(1-in_esop_pool_pct))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <f>Inputs!$B$98</f>
+        <v>Founder D</v>
+      </c>
+      <c r="B8" s="18">
+        <f>in_founder4_time_pct</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <f>in_founder4_salary_forgone_usd</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <f>in_founder4_capital_usd</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>in_founder4_ip_score</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>in_founder4_role_criticality</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>B8*C8+D8+E8*100000+F8*50000</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <f>IF($G$9=0,0,G8/$G$9*(1-in_esop_pool_pct))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G9" s="5">
+        <f>SUM(G5:G8)</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>ESOP pool</t>
+        </is>
+      </c>
+      <c r="H10" s="20">
+        <f>in_esop_pool_pct</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Check (=100%)</t>
+        </is>
+      </c>
+      <c r="H11" s="20">
+        <f>SUM(H5:H8)+H10</f>
         <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Risk PoS (0-1)</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Time of replacement (yrs)</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Time to commercialize (yrs)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cost to develop ($)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Modified RICE</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>(B4*B5*B6*B7*B8*B9)/(B10*B11)</f>
-        <v/>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Reach × Impact × Confidence / Effort (Samyama variant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>WSJF</t>
-        </is>
-      </c>
-      <c r="B15" s="4">
-        <f>(MIN(100,B4*B5*B8/100000)+MAX(0,MIN(1,1/MAX(B9,0.5)))*100+B6*100)/B10</f>
-        <v/>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>(BV + TimeCriticality + RiskReduction) / Duration  [SAFe]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>CD3 ($/yr per yr)</t>
-        </is>
-      </c>
-      <c r="B16" s="5">
-        <f>(B4*B5*B8)/B10</f>
-        <v/>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cost of Delay / Duration  [Reinertsen]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>EMV (USD)</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>B8*(B4*B5)*B9-B11</f>
-        <v/>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>PoS × (annual value × life) − cost</t>
-        </is>
       </c>
     </row>
   </sheetData>
